--- a/Volumetria Relatórios - 2026.xlsx
+++ b/Volumetria Relatórios - 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isabella.chaves\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540DEACA-C65D-4AAA-816F-AA018D05831F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31BD414-3789-4DDD-A6F4-74C5C8735455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Detalhe Completo'!$A$3:$G$451</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Envio Trabalhista'!$A$3:$E$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Painel Geral'!$A$3:$I$258</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Por Categoria'!$A$1:$F$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2789,18 +2790,30 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2815,23 +2828,11 @@
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3147,28 +3148,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
+      <c r="A2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="3" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="59" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="52"/>
@@ -3178,7 +3179,7 @@
       <c r="F4" s="52"/>
     </row>
     <row r="5" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="57" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="52"/>
@@ -3262,7 +3263,7 @@
     </row>
     <row r="11" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="58" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="52"/>
@@ -3275,7 +3276,7 @@
       <c r="B13" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="53" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="52"/>
@@ -3286,7 +3287,7 @@
       <c r="B14" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="53" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="52"/>
@@ -3297,7 +3298,7 @@
       <c r="B15" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="53" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="52"/>
@@ -3308,7 +3309,7 @@
       <c r="B16" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="53" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="52"/>
@@ -3319,7 +3320,7 @@
       <c r="B17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="53" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="52"/>
@@ -3328,7 +3329,7 @@
     </row>
     <row r="19" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="51" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="52"/>
@@ -3339,17 +3340,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C17:F17"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3357,6 +3358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I258"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3371,7 +3373,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="52"/>
@@ -3384,7 +3386,7 @@
       <c r="I1" s="52"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="61" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="52"/>
@@ -3425,7 +3427,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>32</v>
       </c>
@@ -3454,7 +3456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>32</v>
       </c>
@@ -3483,7 +3485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>32</v>
       </c>
@@ -3512,7 +3514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>32</v>
       </c>
@@ -3541,7 +3543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
@@ -3570,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>32</v>
       </c>
@@ -3599,7 +3601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>32</v>
       </c>
@@ -3628,7 +3630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>32</v>
       </c>
@@ -3657,7 +3659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>32</v>
       </c>
@@ -3686,7 +3688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>32</v>
       </c>
@@ -3715,7 +3717,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>32</v>
       </c>
@@ -3744,7 +3746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>32</v>
       </c>
@@ -3773,7 +3775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>32</v>
       </c>
@@ -3802,7 +3804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
@@ -3831,7 +3833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>32</v>
       </c>
@@ -3860,7 +3862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>32</v>
       </c>
@@ -3889,7 +3891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>32</v>
       </c>
@@ -3918,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>32</v>
       </c>
@@ -3947,7 +3949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>32</v>
       </c>
@@ -3976,7 +3978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>32</v>
       </c>
@@ -4005,7 +4007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>32</v>
       </c>
@@ -4034,7 +4036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>32</v>
       </c>
@@ -4063,7 +4065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>32</v>
       </c>
@@ -4092,7 +4094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>32</v>
       </c>
@@ -4121,7 +4123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>32</v>
       </c>
@@ -4150,7 +4152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>32</v>
       </c>
@@ -4179,7 +4181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>32</v>
       </c>
@@ -4208,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>32</v>
       </c>
@@ -4237,7 +4239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>32</v>
       </c>
@@ -4266,7 +4268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
         <v>32</v>
       </c>
@@ -4295,7 +4297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>32</v>
       </c>
@@ -4324,7 +4326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
         <v>32</v>
       </c>
@@ -4353,7 +4355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -4382,7 +4384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>32</v>
       </c>
@@ -4411,7 +4413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
         <v>32</v>
       </c>
@@ -4440,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
         <v>32</v>
       </c>
@@ -4469,7 +4471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>101</v>
       </c>
@@ -4496,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>101</v>
       </c>
@@ -4523,7 +4525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="26" t="s">
         <v>101</v>
       </c>
@@ -4550,7 +4552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>101</v>
       </c>
@@ -4577,7 +4579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="26" t="s">
         <v>101</v>
       </c>
@@ -4604,7 +4606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="26" t="s">
         <v>101</v>
       </c>
@@ -4631,7 +4633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="26" t="s">
         <v>101</v>
       </c>
@@ -4658,7 +4660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="26" t="s">
         <v>101</v>
       </c>
@@ -4685,7 +4687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26" t="s">
         <v>101</v>
       </c>
@@ -4712,7 +4714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="26" t="s">
         <v>101</v>
       </c>
@@ -4739,7 +4741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="26" t="s">
         <v>101</v>
       </c>
@@ -4793,7 +4795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="26" t="s">
         <v>101</v>
       </c>
@@ -4820,7 +4822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="26" t="s">
         <v>101</v>
       </c>
@@ -4847,7 +4849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="26" t="s">
         <v>101</v>
       </c>
@@ -4874,7 +4876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="26" t="s">
         <v>101</v>
       </c>
@@ -4901,7 +4903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="26" t="s">
         <v>101</v>
       </c>
@@ -4928,7 +4930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="26" t="s">
         <v>101</v>
       </c>
@@ -4955,7 +4957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="26" t="s">
         <v>101</v>
       </c>
@@ -4982,7 +4984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="26" t="s">
         <v>101</v>
       </c>
@@ -5009,7 +5011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="26" t="s">
         <v>101</v>
       </c>
@@ -5036,7 +5038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="26" t="s">
         <v>101</v>
       </c>
@@ -5063,7 +5065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="26" t="s">
         <v>101</v>
       </c>
@@ -5090,7 +5092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="26" t="s">
         <v>101</v>
       </c>
@@ -5117,7 +5119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="26" t="s">
         <v>101</v>
       </c>
@@ -5144,7 +5146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="26" t="s">
         <v>101</v>
       </c>
@@ -5171,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="26" t="s">
         <v>101</v>
       </c>
@@ -5198,7 +5200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="26" t="s">
         <v>101</v>
       </c>
@@ -5225,7 +5227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="26" t="s">
         <v>101</v>
       </c>
@@ -5252,7 +5254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="26" t="s">
         <v>101</v>
       </c>
@@ -5279,7 +5281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="26" t="s">
         <v>101</v>
       </c>
@@ -5306,7 +5308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="26" t="s">
         <v>101</v>
       </c>
@@ -5333,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="26" t="s">
         <v>101</v>
       </c>
@@ -5360,7 +5362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="26" t="s">
         <v>101</v>
       </c>
@@ -5387,7 +5389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="26" t="s">
         <v>101</v>
       </c>
@@ -5414,7 +5416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="26" t="s">
         <v>101</v>
       </c>
@@ -5441,7 +5443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="26" t="s">
         <v>101</v>
       </c>
@@ -5468,7 +5470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="26" t="s">
         <v>101</v>
       </c>
@@ -5495,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="26" t="s">
         <v>101</v>
       </c>
@@ -5522,7 +5524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="26" t="s">
         <v>101</v>
       </c>
@@ -5549,7 +5551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="26" t="s">
         <v>101</v>
       </c>
@@ -5576,7 +5578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="26" t="s">
         <v>101</v>
       </c>
@@ -5603,7 +5605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="26" t="s">
         <v>101</v>
       </c>
@@ -5630,7 +5632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="26" t="s">
         <v>101</v>
       </c>
@@ -5657,7 +5659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
         <v>101</v>
       </c>
@@ -5684,7 +5686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="26" t="s">
         <v>101</v>
       </c>
@@ -5711,7 +5713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="26" t="s">
         <v>101</v>
       </c>
@@ -5738,7 +5740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="26" t="s">
         <v>101</v>
       </c>
@@ -5765,7 +5767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="26" t="s">
         <v>101</v>
       </c>
@@ -5792,7 +5794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="26" t="s">
         <v>101</v>
       </c>
@@ -5819,7 +5821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="26" t="s">
         <v>101</v>
       </c>
@@ -5846,7 +5848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="26" t="s">
         <v>101</v>
       </c>
@@ -5873,7 +5875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="26" t="s">
         <v>101</v>
       </c>
@@ -5900,7 +5902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="26" t="s">
         <v>101</v>
       </c>
@@ -5927,7 +5929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="26" t="s">
         <v>101</v>
       </c>
@@ -5954,7 +5956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="33" t="s">
         <v>157</v>
       </c>
@@ -5981,7 +5983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="33" t="s">
         <v>157</v>
       </c>
@@ -6008,7 +6010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="33" t="s">
         <v>157</v>
       </c>
@@ -6035,7 +6037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="33" t="s">
         <v>157</v>
       </c>
@@ -6062,7 +6064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="33" t="s">
         <v>157</v>
       </c>
@@ -6089,7 +6091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="33" t="s">
         <v>157</v>
       </c>
@@ -6116,7 +6118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="33" t="s">
         <v>157</v>
       </c>
@@ -6143,7 +6145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="33" t="s">
         <v>157</v>
       </c>
@@ -6170,7 +6172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="33" t="s">
         <v>157</v>
       </c>
@@ -6197,7 +6199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="33" t="s">
         <v>157</v>
       </c>
@@ -6224,7 +6226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="33" t="s">
         <v>157</v>
       </c>
@@ -6251,7 +6253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="33" t="s">
         <v>157</v>
       </c>
@@ -6278,7 +6280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="33" t="s">
         <v>157</v>
       </c>
@@ -6305,7 +6307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="33" t="s">
         <v>157</v>
       </c>
@@ -6332,7 +6334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="33" t="s">
         <v>157</v>
       </c>
@@ -6359,7 +6361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33" t="s">
         <v>157</v>
       </c>
@@ -6386,7 +6388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="33" t="s">
         <v>157</v>
       </c>
@@ -6413,7 +6415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="33" t="s">
         <v>157</v>
       </c>
@@ -6440,7 +6442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="33" t="s">
         <v>157</v>
       </c>
@@ -6467,7 +6469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="33" t="s">
         <v>157</v>
       </c>
@@ -6494,7 +6496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="33" t="s">
         <v>157</v>
       </c>
@@ -6521,7 +6523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="33" t="s">
         <v>157</v>
       </c>
@@ -6548,7 +6550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="35" t="s">
         <v>188</v>
       </c>
@@ -6575,7 +6577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="35" t="s">
         <v>188</v>
       </c>
@@ -6602,7 +6604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="35" t="s">
         <v>188</v>
       </c>
@@ -6629,7 +6631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="35" t="s">
         <v>188</v>
       </c>
@@ -6656,7 +6658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="35" t="s">
         <v>188</v>
       </c>
@@ -6683,7 +6685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="35" t="s">
         <v>188</v>
       </c>
@@ -6710,7 +6712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="35" t="s">
         <v>188</v>
       </c>
@@ -6737,7 +6739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="35" t="s">
         <v>188</v>
       </c>
@@ -6764,7 +6766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="35" t="s">
         <v>188</v>
       </c>
@@ -6791,7 +6793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="35" t="s">
         <v>188</v>
       </c>
@@ -6818,7 +6820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="35" t="s">
         <v>188</v>
       </c>
@@ -6845,7 +6847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="35" t="s">
         <v>188</v>
       </c>
@@ -6872,7 +6874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="35" t="s">
         <v>188</v>
       </c>
@@ -6899,7 +6901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="35" t="s">
         <v>188</v>
       </c>
@@ -6926,7 +6928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="35" t="s">
         <v>188</v>
       </c>
@@ -6953,7 +6955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="35" t="s">
         <v>188</v>
       </c>
@@ -6980,7 +6982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="35" t="s">
         <v>188</v>
       </c>
@@ -7007,7 +7009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="35" t="s">
         <v>188</v>
       </c>
@@ -7034,7 +7036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="35" t="s">
         <v>188</v>
       </c>
@@ -7061,7 +7063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="35" t="s">
         <v>188</v>
       </c>
@@ -7088,7 +7090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="35" t="s">
         <v>188</v>
       </c>
@@ -7115,7 +7117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="35" t="s">
         <v>188</v>
       </c>
@@ -7142,7 +7144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="35" t="s">
         <v>188</v>
       </c>
@@ -7169,7 +7171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="35" t="s">
         <v>188</v>
       </c>
@@ -7196,7 +7198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="35" t="s">
         <v>188</v>
       </c>
@@ -7223,7 +7225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="35" t="s">
         <v>188</v>
       </c>
@@ -7250,7 +7252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="35" t="s">
         <v>188</v>
       </c>
@@ -7277,7 +7279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="35" t="s">
         <v>188</v>
       </c>
@@ -7304,7 +7306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="35" t="s">
         <v>188</v>
       </c>
@@ -7331,7 +7333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="35" t="s">
         <v>188</v>
       </c>
@@ -7358,7 +7360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="35" t="s">
         <v>188</v>
       </c>
@@ -7385,7 +7387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="35" t="s">
         <v>188</v>
       </c>
@@ -7412,7 +7414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="35" t="s">
         <v>188</v>
       </c>
@@ -7439,7 +7441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="35" t="s">
         <v>188</v>
       </c>
@@ -7466,7 +7468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="35" t="s">
         <v>188</v>
       </c>
@@ -7493,7 +7495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="35" t="s">
         <v>188</v>
       </c>
@@ -7520,7 +7522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="35" t="s">
         <v>188</v>
       </c>
@@ -7547,7 +7549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="35" t="s">
         <v>188</v>
       </c>
@@ -7574,7 +7576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="35" t="s">
         <v>188</v>
       </c>
@@ -7601,7 +7603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="35" t="s">
         <v>188</v>
       </c>
@@ -7628,7 +7630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="35" t="s">
         <v>188</v>
       </c>
@@ -7655,7 +7657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="35" t="s">
         <v>188</v>
       </c>
@@ -7682,7 +7684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="35" t="s">
         <v>188</v>
       </c>
@@ -7709,7 +7711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="35" t="s">
         <v>188</v>
       </c>
@@ -7736,7 +7738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="35" t="s">
         <v>188</v>
       </c>
@@ -7763,7 +7765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="35" t="s">
         <v>188</v>
       </c>
@@ -7790,7 +7792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="35" t="s">
         <v>188</v>
       </c>
@@ -7817,7 +7819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="35" t="s">
         <v>188</v>
       </c>
@@ -7844,7 +7846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="37" t="s">
         <v>254</v>
       </c>
@@ -7871,7 +7873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="37" t="s">
         <v>254</v>
       </c>
@@ -7898,7 +7900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="37" t="s">
         <v>254</v>
       </c>
@@ -7925,7 +7927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="37" t="s">
         <v>254</v>
       </c>
@@ -7952,7 +7954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="37" t="s">
         <v>254</v>
       </c>
@@ -7979,7 +7981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="37" t="s">
         <v>254</v>
       </c>
@@ -8006,7 +8008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="37" t="s">
         <v>254</v>
       </c>
@@ -8033,7 +8035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="37" t="s">
         <v>254</v>
       </c>
@@ -8060,7 +8062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="37" t="s">
         <v>254</v>
       </c>
@@ -8087,7 +8089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="37" t="s">
         <v>254</v>
       </c>
@@ -8114,7 +8116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="37" t="s">
         <v>254</v>
       </c>
@@ -8141,7 +8143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="37" t="s">
         <v>254</v>
       </c>
@@ -8168,7 +8170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="37" t="s">
         <v>254</v>
       </c>
@@ -8195,7 +8197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="37" t="s">
         <v>254</v>
       </c>
@@ -8222,7 +8224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="37" t="s">
         <v>254</v>
       </c>
@@ -8249,7 +8251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="37" t="s">
         <v>254</v>
       </c>
@@ -8276,7 +8278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="37" t="s">
         <v>254</v>
       </c>
@@ -8321,7 +8323,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H182" s="22" t="s">
         <v>38</v>
@@ -8330,7 +8332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="37" t="s">
         <v>254</v>
       </c>
@@ -8357,7 +8359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="37" t="s">
         <v>254</v>
       </c>
@@ -8384,7 +8386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="37" t="s">
         <v>254</v>
       </c>
@@ -8411,7 +8413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="37" t="s">
         <v>254</v>
       </c>
@@ -8438,7 +8440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="37" t="s">
         <v>254</v>
       </c>
@@ -8465,7 +8467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="37" t="s">
         <v>254</v>
       </c>
@@ -8492,7 +8494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="37" t="s">
         <v>254</v>
       </c>
@@ -8519,7 +8521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="37" t="s">
         <v>254</v>
       </c>
@@ -8546,7 +8548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="37" t="s">
         <v>254</v>
       </c>
@@ -8573,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="37" t="s">
         <v>254</v>
       </c>
@@ -8600,7 +8602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="37" t="s">
         <v>254</v>
       </c>
@@ -8627,7 +8629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="37" t="s">
         <v>254</v>
       </c>
@@ -8654,7 +8656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="37" t="s">
         <v>254</v>
       </c>
@@ -8681,7 +8683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="37" t="s">
         <v>254</v>
       </c>
@@ -8708,7 +8710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="37" t="s">
         <v>254</v>
       </c>
@@ -8735,7 +8737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="37" t="s">
         <v>254</v>
       </c>
@@ -8762,7 +8764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="37" t="s">
         <v>254</v>
       </c>
@@ -8789,7 +8791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="37" t="s">
         <v>254</v>
       </c>
@@ -8816,7 +8818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="37" t="s">
         <v>254</v>
       </c>
@@ -8843,7 +8845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="37" t="s">
         <v>254</v>
       </c>
@@ -8870,7 +8872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="37" t="s">
         <v>254</v>
       </c>
@@ -8897,7 +8899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="37" t="s">
         <v>254</v>
       </c>
@@ -8924,7 +8926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="37" t="s">
         <v>254</v>
       </c>
@@ -8951,7 +8953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="37" t="s">
         <v>254</v>
       </c>
@@ -8978,7 +8980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="37" t="s">
         <v>254</v>
       </c>
@@ -9005,7 +9007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="37" t="s">
         <v>254</v>
       </c>
@@ -9032,7 +9034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="37" t="s">
         <v>254</v>
       </c>
@@ -9059,7 +9061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="37" t="s">
         <v>254</v>
       </c>
@@ -9086,7 +9088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="37" t="s">
         <v>254</v>
       </c>
@@ -9113,7 +9115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="37" t="s">
         <v>254</v>
       </c>
@@ -9140,7 +9142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="37" t="s">
         <v>254</v>
       </c>
@@ -9167,7 +9169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="37" t="s">
         <v>254</v>
       </c>
@@ -9194,7 +9196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="37" t="s">
         <v>254</v>
       </c>
@@ -9221,7 +9223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="37" t="s">
         <v>254</v>
       </c>
@@ -9248,7 +9250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="37" t="s">
         <v>254</v>
       </c>
@@ -9275,7 +9277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="37" t="s">
         <v>254</v>
       </c>
@@ -9302,7 +9304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="37" t="s">
         <v>254</v>
       </c>
@@ -9329,7 +9331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="37" t="s">
         <v>254</v>
       </c>
@@ -9356,7 +9358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="37" t="s">
         <v>254</v>
       </c>
@@ -9383,7 +9385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="37" t="s">
         <v>254</v>
       </c>
@@ -9410,7 +9412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="37" t="s">
         <v>254</v>
       </c>
@@ -9437,7 +9439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="37" t="s">
         <v>254</v>
       </c>
@@ -9464,7 +9466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="37" t="s">
         <v>254</v>
       </c>
@@ -9491,7 +9493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="37" t="s">
         <v>254</v>
       </c>
@@ -9518,7 +9520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="37" t="s">
         <v>254</v>
       </c>
@@ -9545,7 +9547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="37" t="s">
         <v>254</v>
       </c>
@@ -9572,7 +9574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="37" t="s">
         <v>254</v>
       </c>
@@ -9599,7 +9601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="37" t="s">
         <v>254</v>
       </c>
@@ -9626,7 +9628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="37" t="s">
         <v>254</v>
       </c>
@@ -9653,7 +9655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="37" t="s">
         <v>254</v>
       </c>
@@ -9680,7 +9682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="37" t="s">
         <v>254</v>
       </c>
@@ -9707,7 +9709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="37" t="s">
         <v>254</v>
       </c>
@@ -9734,7 +9736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="37" t="s">
         <v>254</v>
       </c>
@@ -9761,7 +9763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="37" t="s">
         <v>254</v>
       </c>
@@ -9788,7 +9790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="37" t="s">
         <v>254</v>
       </c>
@@ -9815,7 +9817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="37" t="s">
         <v>254</v>
       </c>
@@ -9842,7 +9844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="37" t="s">
         <v>254</v>
       </c>
@@ -9869,7 +9871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="37" t="s">
         <v>254</v>
       </c>
@@ -9896,7 +9898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="37" t="s">
         <v>254</v>
       </c>
@@ -9923,7 +9925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="37" t="s">
         <v>254</v>
       </c>
@@ -9950,7 +9952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="37" t="s">
         <v>254</v>
       </c>
@@ -9977,7 +9979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="37" t="s">
         <v>254</v>
       </c>
@@ -10004,7 +10006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="37" t="s">
         <v>254</v>
       </c>
@@ -10031,7 +10033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="37" t="s">
         <v>254</v>
       </c>
@@ -10058,7 +10060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="37" t="s">
         <v>254</v>
       </c>
@@ -10085,7 +10087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="37" t="s">
         <v>254</v>
       </c>
@@ -10112,7 +10114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="37" t="s">
         <v>254</v>
       </c>
@@ -10139,7 +10141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="37" t="s">
         <v>254</v>
       </c>
@@ -10166,7 +10168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="37" t="s">
         <v>254</v>
       </c>
@@ -10193,7 +10195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="37" t="s">
         <v>254</v>
       </c>
@@ -10220,7 +10222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="37" t="s">
         <v>254</v>
       </c>
@@ -10247,7 +10249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="37" t="s">
         <v>254</v>
       </c>
@@ -10274,7 +10276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="37" t="s">
         <v>254</v>
       </c>
@@ -10301,7 +10303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="37" t="s">
         <v>254</v>
       </c>
@@ -10328,7 +10330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="37" t="s">
         <v>254</v>
       </c>
@@ -10355,7 +10357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="37" t="s">
         <v>254</v>
       </c>
@@ -10383,7 +10385,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I258" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A3:I258" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Daltez"/>
+        <filter val="Daltez - Bimestral"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -10406,7 +10415,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>354</v>
       </c>
       <c r="B1" s="52"/>
@@ -10416,7 +10425,7 @@
       <c r="F1" s="52"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="63" t="s">
         <v>355</v>
       </c>
       <c r="B2" s="52"/>
@@ -11167,7 +11176,7 @@
     </row>
     <row r="40" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="60" t="s">
+      <c r="A42" s="64" t="s">
         <v>362</v>
       </c>
       <c r="B42" s="52"/>
@@ -12298,7 +12307,7 @@
     </row>
     <row r="99" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="62" t="s">
+      <c r="A101" s="66" t="s">
         <v>364</v>
       </c>
       <c r="B101" s="52"/>
@@ -12769,7 +12778,7 @@
     </row>
     <row r="125" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="61" t="s">
+      <c r="A127" s="65" t="s">
         <v>374</v>
       </c>
       <c r="B127" s="52"/>
@@ -13760,7 +13769,7 @@
     </row>
     <row r="177" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="179" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="63" t="s">
+      <c r="A179" s="62" t="s">
         <v>380</v>
       </c>
       <c r="B179" s="52"/>
@@ -14157,13 +14166,13 @@
         <v>277</v>
       </c>
       <c r="C199" s="22" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D199" s="24" t="s">
         <v>36</v>
       </c>
       <c r="E199" s="25" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="F199" s="26">
         <v>1</v>
@@ -15671,6 +15680,13 @@
     </row>
     <row r="275" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="A1:F39" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="0" showButton="0"/>
+    <filterColumn colId="1" showButton="0"/>
+    <filterColumn colId="2" showButton="0"/>
+    <filterColumn colId="3" showButton="0"/>
+    <filterColumn colId="4" showButton="0"/>
+  </autoFilter>
   <mergeCells count="6">
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="A2:F2"/>
@@ -15685,6 +15701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G451"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15698,7 +15715,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>381</v>
       </c>
       <c r="B1" s="52"/>
@@ -15709,7 +15726,7 @@
       <c r="G1" s="52"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="61" t="s">
         <v>382</v>
       </c>
       <c r="B2" s="52"/>
@@ -15742,7 +15759,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
         <v>157</v>
       </c>
@@ -15765,7 +15782,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>157</v>
       </c>
@@ -15788,7 +15805,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
         <v>157</v>
       </c>
@@ -15811,7 +15828,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>157</v>
       </c>
@@ -15834,7 +15851,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>157</v>
       </c>
@@ -15857,7 +15874,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>101</v>
       </c>
@@ -15880,7 +15897,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>101</v>
       </c>
@@ -15903,7 +15920,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="s">
         <v>254</v>
       </c>
@@ -15926,7 +15943,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
         <v>188</v>
       </c>
@@ -15949,7 +15966,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
         <v>188</v>
       </c>
@@ -15972,7 +15989,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
         <v>101</v>
       </c>
@@ -15995,7 +16012,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
         <v>101</v>
       </c>
@@ -16018,7 +16035,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
         <v>157</v>
       </c>
@@ -16041,7 +16058,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>157</v>
       </c>
@@ -16064,7 +16081,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
         <v>157</v>
       </c>
@@ -16087,7 +16104,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>157</v>
       </c>
@@ -16110,7 +16127,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
         <v>157</v>
       </c>
@@ -16133,7 +16150,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>157</v>
       </c>
@@ -16156,7 +16173,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
         <v>254</v>
       </c>
@@ -16177,7 +16194,7 @@
       </c>
       <c r="G22" s="22"/>
     </row>
-    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
         <v>101</v>
       </c>
@@ -16200,7 +16217,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="36" t="s">
         <v>188</v>
       </c>
@@ -16223,7 +16240,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="36" t="s">
         <v>188</v>
       </c>
@@ -16246,7 +16263,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
         <v>101</v>
       </c>
@@ -16269,7 +16286,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="38" t="s">
         <v>254</v>
       </c>
@@ -16292,7 +16309,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
         <v>157</v>
       </c>
@@ -16315,7 +16332,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34" t="s">
         <v>157</v>
       </c>
@@ -16338,7 +16355,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="38" t="s">
         <v>254</v>
       </c>
@@ -16361,7 +16378,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36" t="s">
         <v>188</v>
       </c>
@@ -16384,7 +16401,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="36" t="s">
         <v>188</v>
       </c>
@@ -16407,7 +16424,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="32" t="s">
         <v>101</v>
       </c>
@@ -16430,7 +16447,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="38" t="s">
         <v>254</v>
       </c>
@@ -16453,7 +16470,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="38" t="s">
         <v>254</v>
       </c>
@@ -16476,7 +16493,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20" t="s">
         <v>32</v>
       </c>
@@ -16499,7 +16516,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
         <v>32</v>
       </c>
@@ -16522,7 +16539,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20" t="s">
         <v>32</v>
       </c>
@@ -16545,7 +16562,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20" t="s">
         <v>32</v>
       </c>
@@ -16568,7 +16585,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="38" t="s">
         <v>254</v>
       </c>
@@ -16591,7 +16608,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="36" t="s">
         <v>188</v>
       </c>
@@ -16614,7 +16631,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="36" t="s">
         <v>188</v>
       </c>
@@ -16637,7 +16654,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="36" t="s">
         <v>188</v>
       </c>
@@ -16660,7 +16677,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="34" t="s">
         <v>157</v>
       </c>
@@ -16683,7 +16700,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="34" t="s">
         <v>157</v>
       </c>
@@ -16706,7 +16723,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
         <v>32</v>
       </c>
@@ -16729,7 +16746,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="38" t="s">
         <v>254</v>
       </c>
@@ -16752,7 +16769,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="34" t="s">
         <v>157</v>
       </c>
@@ -16775,7 +16792,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="34" t="s">
         <v>157</v>
       </c>
@@ -16798,7 +16815,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="34" t="s">
         <v>157</v>
       </c>
@@ -16821,7 +16838,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="34" t="s">
         <v>157</v>
       </c>
@@ -16844,7 +16861,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="36" t="s">
         <v>188</v>
       </c>
@@ -16867,7 +16884,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="36" t="s">
         <v>188</v>
       </c>
@@ -16890,7 +16907,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="38" t="s">
         <v>254</v>
       </c>
@@ -16913,7 +16930,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="36" t="s">
         <v>188</v>
       </c>
@@ -16936,7 +16953,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="36" t="s">
         <v>188</v>
       </c>
@@ -16959,7 +16976,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="36" t="s">
         <v>188</v>
       </c>
@@ -16982,7 +16999,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="36" t="s">
         <v>188</v>
       </c>
@@ -17005,7 +17022,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="36" t="s">
         <v>188</v>
       </c>
@@ -17028,7 +17045,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="36" t="s">
         <v>188</v>
       </c>
@@ -17051,7 +17068,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="36" t="s">
         <v>188</v>
       </c>
@@ -17074,7 +17091,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="36" t="s">
         <v>188</v>
       </c>
@@ -17097,7 +17114,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="36" t="s">
         <v>188</v>
       </c>
@@ -17120,7 +17137,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="38" t="s">
         <v>254</v>
       </c>
@@ -17143,7 +17160,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="36" t="s">
         <v>188</v>
       </c>
@@ -17166,7 +17183,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="36" t="s">
         <v>188</v>
       </c>
@@ -17189,7 +17206,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="36" t="s">
         <v>188</v>
       </c>
@@ -17212,7 +17229,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="36" t="s">
         <v>188</v>
       </c>
@@ -17235,7 +17252,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="38" t="s">
         <v>254</v>
       </c>
@@ -17258,7 +17275,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="38" t="s">
         <v>254</v>
       </c>
@@ -17281,7 +17298,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="38" t="s">
         <v>254</v>
       </c>
@@ -17304,7 +17321,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="38" t="s">
         <v>254</v>
       </c>
@@ -17327,7 +17344,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="36" t="s">
         <v>188</v>
       </c>
@@ -17350,7 +17367,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="36" t="s">
         <v>188</v>
       </c>
@@ -17373,7 +17390,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="38" t="s">
         <v>254</v>
       </c>
@@ -17396,7 +17413,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="32" t="s">
         <v>101</v>
       </c>
@@ -17419,7 +17436,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="20" t="s">
         <v>32</v>
       </c>
@@ -17442,7 +17459,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="32" t="s">
         <v>101</v>
       </c>
@@ -17465,7 +17482,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="32" t="s">
         <v>101</v>
       </c>
@@ -17488,7 +17505,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="36" t="s">
         <v>188</v>
       </c>
@@ -17511,7 +17528,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="36" t="s">
         <v>188</v>
       </c>
@@ -17534,7 +17551,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="36" t="s">
         <v>188</v>
       </c>
@@ -17557,7 +17574,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="34" t="s">
         <v>157</v>
       </c>
@@ -17580,7 +17597,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="34" t="s">
         <v>157</v>
       </c>
@@ -17603,7 +17620,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="34" t="s">
         <v>157</v>
       </c>
@@ -17626,7 +17643,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="32" t="s">
         <v>101</v>
       </c>
@@ -17649,7 +17666,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="36" t="s">
         <v>188</v>
       </c>
@@ -17672,7 +17689,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="36" t="s">
         <v>188</v>
       </c>
@@ -17695,7 +17712,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="38" t="s">
         <v>254</v>
       </c>
@@ -17718,7 +17735,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="38" t="s">
         <v>254</v>
       </c>
@@ -17778,7 +17795,7 @@
         <v>36</v>
       </c>
       <c r="E92" s="22" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="F92" s="43" t="s">
         <v>469</v>
@@ -17810,7 +17827,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="38" t="s">
         <v>254</v>
       </c>
@@ -17833,7 +17850,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="38" t="s">
         <v>254</v>
       </c>
@@ -17856,7 +17873,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="38" t="s">
         <v>254</v>
       </c>
@@ -17879,7 +17896,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="38" t="s">
         <v>254</v>
       </c>
@@ -17902,7 +17919,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="36" t="s">
         <v>188</v>
       </c>
@@ -17925,7 +17942,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="36" t="s">
         <v>188</v>
       </c>
@@ -17948,7 +17965,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="36" t="s">
         <v>188</v>
       </c>
@@ -17971,7 +17988,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="32" t="s">
         <v>101</v>
       </c>
@@ -17994,7 +18011,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="32" t="s">
         <v>101</v>
       </c>
@@ -18017,7 +18034,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="38" t="s">
         <v>254</v>
       </c>
@@ -18040,7 +18057,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="38" t="s">
         <v>254</v>
       </c>
@@ -18063,7 +18080,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="32" t="s">
         <v>101</v>
       </c>
@@ -18086,7 +18103,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="36" t="s">
         <v>188</v>
       </c>
@@ -18109,7 +18126,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="36" t="s">
         <v>188</v>
       </c>
@@ -18132,7 +18149,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="36" t="s">
         <v>188</v>
       </c>
@@ -18155,7 +18172,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="36" t="s">
         <v>188</v>
       </c>
@@ -18178,7 +18195,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="36" t="s">
         <v>188</v>
       </c>
@@ -18201,7 +18218,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="38" t="s">
         <v>254</v>
       </c>
@@ -18224,7 +18241,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="36" t="s">
         <v>188</v>
       </c>
@@ -18247,7 +18264,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="36" t="s">
         <v>188</v>
       </c>
@@ -18270,7 +18287,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="36" t="s">
         <v>188</v>
       </c>
@@ -18293,7 +18310,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="36" t="s">
         <v>188</v>
       </c>
@@ -18316,7 +18333,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="36" t="s">
         <v>188</v>
       </c>
@@ -18339,7 +18356,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="36" t="s">
         <v>188</v>
       </c>
@@ -18362,7 +18379,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="36" t="s">
         <v>188</v>
       </c>
@@ -18385,7 +18402,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="36" t="s">
         <v>188</v>
       </c>
@@ -18408,7 +18425,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="36" t="s">
         <v>188</v>
       </c>
@@ -18431,7 +18448,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="36" t="s">
         <v>188</v>
       </c>
@@ -18454,7 +18471,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="36" t="s">
         <v>188</v>
       </c>
@@ -18477,7 +18494,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="36" t="s">
         <v>188</v>
       </c>
@@ -18500,7 +18517,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="20" t="s">
         <v>32</v>
       </c>
@@ -18523,7 +18540,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="38" t="s">
         <v>254</v>
       </c>
@@ -18546,7 +18563,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="32" t="s">
         <v>101</v>
       </c>
@@ -18567,7 +18584,7 @@
       </c>
       <c r="G126" s="28"/>
     </row>
-    <row r="127" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="34" t="s">
         <v>157</v>
       </c>
@@ -18590,7 +18607,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="34" t="s">
         <v>157</v>
       </c>
@@ -18613,7 +18630,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="38" t="s">
         <v>254</v>
       </c>
@@ -18636,7 +18653,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="38" t="s">
         <v>254</v>
       </c>
@@ -18659,7 +18676,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="20" t="s">
         <v>32</v>
       </c>
@@ -18682,7 +18699,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="38" t="s">
         <v>254</v>
       </c>
@@ -18705,7 +18722,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="36" t="s">
         <v>188</v>
       </c>
@@ -18728,7 +18745,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="36" t="s">
         <v>188</v>
       </c>
@@ -18751,7 +18768,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="32" t="s">
         <v>101</v>
       </c>
@@ -18774,7 +18791,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="20" t="s">
         <v>32</v>
       </c>
@@ -18797,7 +18814,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="20" t="s">
         <v>32</v>
       </c>
@@ -18820,7 +18837,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="20" t="s">
         <v>32</v>
       </c>
@@ -18843,7 +18860,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="20" t="s">
         <v>32</v>
       </c>
@@ -18866,7 +18883,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="20" t="s">
         <v>32</v>
       </c>
@@ -18889,7 +18906,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="20" t="s">
         <v>32</v>
       </c>
@@ -18912,7 +18929,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="20" t="s">
         <v>32</v>
       </c>
@@ -18935,7 +18952,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="20" t="s">
         <v>32</v>
       </c>
@@ -18958,7 +18975,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="20" t="s">
         <v>32</v>
       </c>
@@ -18981,7 +18998,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="20" t="s">
         <v>32</v>
       </c>
@@ -19004,7 +19021,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="32" t="s">
         <v>101</v>
       </c>
@@ -19027,7 +19044,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="36" t="s">
         <v>188</v>
       </c>
@@ -19050,7 +19067,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="36" t="s">
         <v>188</v>
       </c>
@@ -19073,7 +19090,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="36" t="s">
         <v>188</v>
       </c>
@@ -19096,7 +19113,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="36" t="s">
         <v>188</v>
       </c>
@@ -19119,7 +19136,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="34" t="s">
         <v>157</v>
       </c>
@@ -19142,7 +19159,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="34" t="s">
         <v>157</v>
       </c>
@@ -19165,7 +19182,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="20" t="s">
         <v>32</v>
       </c>
@@ -19188,7 +19205,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="20" t="s">
         <v>32</v>
       </c>
@@ -19211,7 +19228,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="20" t="s">
         <v>32</v>
       </c>
@@ -19234,7 +19251,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="20" t="s">
         <v>32</v>
       </c>
@@ -19257,7 +19274,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="20" t="s">
         <v>32</v>
       </c>
@@ -19280,7 +19297,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="20" t="s">
         <v>32</v>
       </c>
@@ -19303,7 +19320,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="20" t="s">
         <v>32</v>
       </c>
@@ -19326,7 +19343,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="20" t="s">
         <v>32</v>
       </c>
@@ -19349,7 +19366,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="20" t="s">
         <v>32</v>
       </c>
@@ -19372,7 +19389,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="20" t="s">
         <v>32</v>
       </c>
@@ -19395,7 +19412,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="20" t="s">
         <v>32</v>
       </c>
@@ -19418,7 +19435,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="20" t="s">
         <v>32</v>
       </c>
@@ -19441,7 +19458,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="20" t="s">
         <v>32</v>
       </c>
@@ -19464,7 +19481,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="20" t="s">
         <v>32</v>
       </c>
@@ -19487,7 +19504,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="20" t="s">
         <v>32</v>
       </c>
@@ -19510,7 +19527,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="36" t="s">
         <v>188</v>
       </c>
@@ -19533,7 +19550,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="36" t="s">
         <v>188</v>
       </c>
@@ -19556,7 +19573,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="20" t="s">
         <v>32</v>
       </c>
@@ -19579,7 +19596,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="20" t="s">
         <v>32</v>
       </c>
@@ -19602,7 +19619,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="20" t="s">
         <v>32</v>
       </c>
@@ -19625,7 +19642,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="20" t="s">
         <v>32</v>
       </c>
@@ -19648,7 +19665,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="20" t="s">
         <v>32</v>
       </c>
@@ -19671,7 +19688,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="20" t="s">
         <v>32</v>
       </c>
@@ -19694,7 +19711,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="20" t="s">
         <v>32</v>
       </c>
@@ -19717,7 +19734,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="20" t="s">
         <v>32</v>
       </c>
@@ -19740,7 +19757,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="38" t="s">
         <v>254</v>
       </c>
@@ -19763,7 +19780,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="32" t="s">
         <v>101</v>
       </c>
@@ -19786,7 +19803,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="38" t="s">
         <v>254</v>
       </c>
@@ -19809,7 +19826,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="38" t="s">
         <v>254</v>
       </c>
@@ -19832,7 +19849,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="20" t="s">
         <v>32</v>
       </c>
@@ -19855,7 +19872,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="20" t="s">
         <v>32</v>
       </c>
@@ -19878,7 +19895,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="20" t="s">
         <v>32</v>
       </c>
@@ -19901,7 +19918,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="20" t="s">
         <v>32</v>
       </c>
@@ -19924,7 +19941,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="38" t="s">
         <v>254</v>
       </c>
@@ -19947,7 +19964,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="38" t="s">
         <v>254</v>
       </c>
@@ -19970,7 +19987,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="38" t="s">
         <v>254</v>
       </c>
@@ -19993,7 +20010,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="38" t="s">
         <v>254</v>
       </c>
@@ -20016,7 +20033,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="38" t="s">
         <v>254</v>
       </c>
@@ -20039,7 +20056,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="38" t="s">
         <v>254</v>
       </c>
@@ -20062,7 +20079,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="32" t="s">
         <v>101</v>
       </c>
@@ -20085,7 +20102,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="20" t="s">
         <v>32</v>
       </c>
@@ -20108,7 +20125,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="20" t="s">
         <v>32</v>
       </c>
@@ -20131,7 +20148,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="20" t="s">
         <v>32</v>
       </c>
@@ -20154,7 +20171,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="34" t="s">
         <v>157</v>
       </c>
@@ -20177,7 +20194,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="34" t="s">
         <v>157</v>
       </c>
@@ -20200,7 +20217,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="34" t="s">
         <v>157</v>
       </c>
@@ -20223,7 +20240,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="34" t="s">
         <v>157</v>
       </c>
@@ -20246,7 +20263,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="38" t="s">
         <v>254</v>
       </c>
@@ -20269,7 +20286,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="38" t="s">
         <v>254</v>
       </c>
@@ -20292,7 +20309,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="36" t="s">
         <v>188</v>
       </c>
@@ -20315,7 +20332,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="36" t="s">
         <v>188</v>
       </c>
@@ -20338,7 +20355,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="38" t="s">
         <v>254</v>
       </c>
@@ -20361,7 +20378,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="36" t="s">
         <v>188</v>
       </c>
@@ -20384,7 +20401,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="36" t="s">
         <v>188</v>
       </c>
@@ -20407,7 +20424,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="32" t="s">
         <v>101</v>
       </c>
@@ -20430,7 +20447,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="36" t="s">
         <v>188</v>
       </c>
@@ -20453,7 +20470,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="36" t="s">
         <v>188</v>
       </c>
@@ -20476,7 +20493,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="32" t="s">
         <v>101</v>
       </c>
@@ -20499,7 +20516,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="32" t="s">
         <v>101</v>
       </c>
@@ -20522,7 +20539,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="36" t="s">
         <v>188</v>
       </c>
@@ -20545,7 +20562,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="36" t="s">
         <v>188</v>
       </c>
@@ -20568,7 +20585,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="36" t="s">
         <v>188</v>
       </c>
@@ -20591,7 +20608,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="36" t="s">
         <v>188</v>
       </c>
@@ -20614,7 +20631,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="32" t="s">
         <v>101</v>
       </c>
@@ -20637,7 +20654,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="38" t="s">
         <v>254</v>
       </c>
@@ -20660,7 +20677,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="38" t="s">
         <v>254</v>
       </c>
@@ -20683,7 +20700,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="38" t="s">
         <v>254</v>
       </c>
@@ -20706,7 +20723,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="20" t="s">
         <v>32</v>
       </c>
@@ -20729,7 +20746,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="20" t="s">
         <v>32</v>
       </c>
@@ -20752,7 +20769,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="20" t="s">
         <v>32</v>
       </c>
@@ -20775,7 +20792,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="20" t="s">
         <v>32</v>
       </c>
@@ -20798,7 +20815,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="20" t="s">
         <v>32</v>
       </c>
@@ -20821,7 +20838,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="38" t="s">
         <v>254</v>
       </c>
@@ -20844,7 +20861,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="32" t="s">
         <v>101</v>
       </c>
@@ -20867,7 +20884,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="32" t="s">
         <v>101</v>
       </c>
@@ -20890,7 +20907,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="34" t="s">
         <v>157</v>
       </c>
@@ -20913,7 +20930,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="34" t="s">
         <v>157</v>
       </c>
@@ -20936,7 +20953,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="36" t="s">
         <v>188</v>
       </c>
@@ -20959,7 +20976,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="36" t="s">
         <v>188</v>
       </c>
@@ -20982,7 +20999,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="36" t="s">
         <v>188</v>
       </c>
@@ -21005,7 +21022,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="36" t="s">
         <v>188</v>
       </c>
@@ -21028,7 +21045,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="36" t="s">
         <v>188</v>
       </c>
@@ -21051,7 +21068,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="20" t="s">
         <v>32</v>
       </c>
@@ -21074,7 +21091,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="20" t="s">
         <v>32</v>
       </c>
@@ -21097,7 +21114,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="20" t="s">
         <v>32</v>
       </c>
@@ -21120,7 +21137,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="20" t="s">
         <v>32</v>
       </c>
@@ -21143,7 +21160,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="20" t="s">
         <v>32</v>
       </c>
@@ -21166,7 +21183,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="20" t="s">
         <v>32</v>
       </c>
@@ -21189,7 +21206,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="20" t="s">
         <v>32</v>
       </c>
@@ -21212,7 +21229,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="20" t="s">
         <v>32</v>
       </c>
@@ -21235,7 +21252,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="20" t="s">
         <v>32</v>
       </c>
@@ -21258,7 +21275,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="20" t="s">
         <v>32</v>
       </c>
@@ -21281,7 +21298,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="32" t="s">
         <v>101</v>
       </c>
@@ -21304,7 +21321,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="32" t="s">
         <v>101</v>
       </c>
@@ -21327,7 +21344,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="38" t="s">
         <v>254</v>
       </c>
@@ -21350,7 +21367,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="20" t="s">
         <v>32</v>
       </c>
@@ -21373,7 +21390,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="20" t="s">
         <v>32</v>
       </c>
@@ -21396,7 +21413,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="20" t="s">
         <v>32</v>
       </c>
@@ -21419,7 +21436,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="20" t="s">
         <v>32</v>
       </c>
@@ -21442,7 +21459,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="20" t="s">
         <v>32</v>
       </c>
@@ -21465,7 +21482,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="32" t="s">
         <v>101</v>
       </c>
@@ -21488,7 +21505,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="38" t="s">
         <v>254</v>
       </c>
@@ -21511,7 +21528,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="20" t="s">
         <v>32</v>
       </c>
@@ -21534,7 +21551,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="20" t="s">
         <v>32</v>
       </c>
@@ -21557,7 +21574,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="20" t="s">
         <v>32</v>
       </c>
@@ -21580,7 +21597,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="34" t="s">
         <v>157</v>
       </c>
@@ -21603,7 +21620,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="34" t="s">
         <v>157</v>
       </c>
@@ -21626,7 +21643,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="38" t="s">
         <v>254</v>
       </c>
@@ -21649,7 +21666,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="38" t="s">
         <v>254</v>
       </c>
@@ -21672,7 +21689,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="36" t="s">
         <v>188</v>
       </c>
@@ -21695,7 +21712,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="36" t="s">
         <v>188</v>
       </c>
@@ -21718,7 +21735,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="32" t="s">
         <v>101</v>
       </c>
@@ -21741,7 +21758,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="36" t="s">
         <v>188</v>
       </c>
@@ -21764,7 +21781,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="36" t="s">
         <v>188</v>
       </c>
@@ -21787,7 +21804,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="38" t="s">
         <v>254</v>
       </c>
@@ -21810,7 +21827,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="38" t="s">
         <v>254</v>
       </c>
@@ -21833,7 +21850,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="38" t="s">
         <v>254</v>
       </c>
@@ -21856,7 +21873,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="20" t="s">
         <v>32</v>
       </c>
@@ -21879,7 +21896,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="20" t="s">
         <v>32</v>
       </c>
@@ -21902,7 +21919,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="20" t="s">
         <v>32</v>
       </c>
@@ -21925,7 +21942,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="20" t="s">
         <v>32</v>
       </c>
@@ -21948,7 +21965,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="20" t="s">
         <v>32</v>
       </c>
@@ -21971,7 +21988,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="32" t="s">
         <v>101</v>
       </c>
@@ -21994,7 +22011,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="38" t="s">
         <v>254</v>
       </c>
@@ -22017,7 +22034,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="36" t="s">
         <v>188</v>
       </c>
@@ -22040,7 +22057,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="36" t="s">
         <v>188</v>
       </c>
@@ -22063,7 +22080,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="34" t="s">
         <v>157</v>
       </c>
@@ -22086,7 +22103,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="34" t="s">
         <v>157</v>
       </c>
@@ -22109,7 +22126,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="34" t="s">
         <v>157</v>
       </c>
@@ -22132,7 +22149,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="38" t="s">
         <v>254</v>
       </c>
@@ -22155,7 +22172,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="38" t="s">
         <v>254</v>
       </c>
@@ -22178,7 +22195,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="36" t="s">
         <v>188</v>
       </c>
@@ -22201,7 +22218,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="36" t="s">
         <v>188</v>
       </c>
@@ -22224,7 +22241,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="36" t="s">
         <v>188</v>
       </c>
@@ -22247,7 +22264,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="36" t="s">
         <v>188</v>
       </c>
@@ -22270,7 +22287,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="36" t="s">
         <v>188</v>
       </c>
@@ -22293,7 +22310,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="36" t="s">
         <v>188</v>
       </c>
@@ -22316,7 +22333,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="38" t="s">
         <v>254</v>
       </c>
@@ -22339,7 +22356,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="32" t="s">
         <v>101</v>
       </c>
@@ -22362,7 +22379,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="38" t="s">
         <v>254</v>
       </c>
@@ -22385,7 +22402,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="38" t="s">
         <v>254</v>
       </c>
@@ -22408,7 +22425,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="38" t="s">
         <v>254</v>
       </c>
@@ -22431,7 +22448,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="38" t="s">
         <v>254</v>
       </c>
@@ -22454,7 +22471,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="38" t="s">
         <v>254</v>
       </c>
@@ -22477,7 +22494,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="32" t="s">
         <v>101</v>
       </c>
@@ -22500,7 +22517,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="38" t="s">
         <v>254</v>
       </c>
@@ -22523,7 +22540,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="36" t="s">
         <v>188</v>
       </c>
@@ -22546,7 +22563,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="36" t="s">
         <v>188</v>
       </c>
@@ -22569,7 +22586,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="36" t="s">
         <v>188</v>
       </c>
@@ -22592,7 +22609,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="36" t="s">
         <v>188</v>
       </c>
@@ -22615,7 +22632,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="34" t="s">
         <v>157</v>
       </c>
@@ -22638,7 +22655,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="34" t="s">
         <v>157</v>
       </c>
@@ -22661,7 +22678,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="38" t="s">
         <v>254</v>
       </c>
@@ -22684,7 +22701,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="36" t="s">
         <v>188</v>
       </c>
@@ -22707,7 +22724,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="36" t="s">
         <v>188</v>
       </c>
@@ -22730,7 +22747,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="36" t="s">
         <v>188</v>
       </c>
@@ -22753,7 +22770,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="36" t="s">
         <v>188</v>
       </c>
@@ -22776,7 +22793,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="38" t="s">
         <v>254</v>
       </c>
@@ -22822,7 +22839,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="36" t="s">
         <v>188</v>
       </c>
@@ -22845,7 +22862,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="36" t="s">
         <v>188</v>
       </c>
@@ -22868,7 +22885,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="32" t="s">
         <v>101</v>
       </c>
@@ -22891,7 +22908,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="38" t="s">
         <v>254</v>
       </c>
@@ -22914,7 +22931,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="38" t="s">
         <v>254</v>
       </c>
@@ -22937,7 +22954,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="36" t="s">
         <v>188</v>
       </c>
@@ -22960,7 +22977,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="36" t="s">
         <v>188</v>
       </c>
@@ -22983,7 +23000,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="38" t="s">
         <v>254</v>
       </c>
@@ -23006,7 +23023,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="38" t="s">
         <v>254</v>
       </c>
@@ -23029,7 +23046,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="34" t="s">
         <v>157</v>
       </c>
@@ -23052,7 +23069,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="34" t="s">
         <v>157</v>
       </c>
@@ -23075,7 +23092,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="36" t="s">
         <v>188</v>
       </c>
@@ -23098,7 +23115,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="36" t="s">
         <v>188</v>
       </c>
@@ -23121,7 +23138,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="34" t="s">
         <v>157</v>
       </c>
@@ -23144,7 +23161,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="34" t="s">
         <v>157</v>
       </c>
@@ -23167,7 +23184,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="36" t="s">
         <v>188</v>
       </c>
@@ -23190,7 +23207,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="36" t="s">
         <v>188</v>
       </c>
@@ -23213,7 +23230,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="38" t="s">
         <v>254</v>
       </c>
@@ -23236,7 +23253,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="32" t="s">
         <v>101</v>
       </c>
@@ -23259,7 +23276,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="38" t="s">
         <v>254</v>
       </c>
@@ -23282,7 +23299,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="32" t="s">
         <v>101</v>
       </c>
@@ -23305,7 +23322,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="32" t="s">
         <v>101</v>
       </c>
@@ -23328,7 +23345,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="32" t="s">
         <v>101</v>
       </c>
@@ -23351,7 +23368,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="32" t="s">
         <v>101</v>
       </c>
@@ -23374,7 +23391,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="20" t="s">
         <v>32</v>
       </c>
@@ -23397,7 +23414,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="20" t="s">
         <v>32</v>
       </c>
@@ -23420,7 +23437,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="32" t="s">
         <v>101</v>
       </c>
@@ -23443,7 +23460,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="32" t="s">
         <v>101</v>
       </c>
@@ -23466,7 +23483,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="38" t="s">
         <v>254</v>
       </c>
@@ -23489,7 +23506,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="38" t="s">
         <v>254</v>
       </c>
@@ -23512,7 +23529,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="38" t="s">
         <v>254</v>
       </c>
@@ -23535,7 +23552,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="36" t="s">
         <v>188</v>
       </c>
@@ -23558,7 +23575,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="36" t="s">
         <v>188</v>
       </c>
@@ -23581,7 +23598,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="32" t="s">
         <v>101</v>
       </c>
@@ -23604,7 +23621,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="20" t="s">
         <v>32</v>
       </c>
@@ -23627,7 +23644,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="20" t="s">
         <v>32</v>
       </c>
@@ -23650,7 +23667,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="20" t="s">
         <v>32</v>
       </c>
@@ -23673,7 +23690,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="20" t="s">
         <v>32</v>
       </c>
@@ -23696,7 +23713,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="20" t="s">
         <v>32</v>
       </c>
@@ -23719,7 +23736,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="36" t="s">
         <v>188</v>
       </c>
@@ -23742,7 +23759,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="36" t="s">
         <v>188</v>
       </c>
@@ -23765,7 +23782,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="38" t="s">
         <v>254</v>
       </c>
@@ -23788,7 +23805,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="38" t="s">
         <v>254</v>
       </c>
@@ -23811,7 +23828,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="36" t="s">
         <v>188</v>
       </c>
@@ -23834,7 +23851,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="36" t="s">
         <v>188</v>
       </c>
@@ -23857,7 +23874,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="36" t="s">
         <v>188</v>
       </c>
@@ -23880,7 +23897,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="38" t="s">
         <v>254</v>
       </c>
@@ -23903,7 +23920,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="34" t="s">
         <v>157</v>
       </c>
@@ -23926,7 +23943,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="34" t="s">
         <v>157</v>
       </c>
@@ -23949,7 +23966,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="34" t="s">
         <v>157</v>
       </c>
@@ -23972,7 +23989,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="34" t="s">
         <v>157</v>
       </c>
@@ -23995,7 +24012,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="34" t="s">
         <v>157</v>
       </c>
@@ -24018,7 +24035,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="34" t="s">
         <v>157</v>
       </c>
@@ -24041,7 +24058,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="20" t="s">
         <v>32</v>
       </c>
@@ -24064,7 +24081,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="20" t="s">
         <v>32</v>
       </c>
@@ -24087,7 +24104,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="38" t="s">
         <v>254</v>
       </c>
@@ -24110,7 +24127,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="38" t="s">
         <v>254</v>
       </c>
@@ -24133,7 +24150,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="38" t="s">
         <v>254</v>
       </c>
@@ -24156,7 +24173,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="32" t="s">
         <v>101</v>
       </c>
@@ -24179,7 +24196,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="38" t="s">
         <v>254</v>
       </c>
@@ -24202,7 +24219,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="32" t="s">
         <v>101</v>
       </c>
@@ -24225,7 +24242,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="36" t="s">
         <v>188</v>
       </c>
@@ -24248,7 +24265,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="36" t="s">
         <v>188</v>
       </c>
@@ -24271,7 +24288,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="36" t="s">
         <v>188</v>
       </c>
@@ -24294,7 +24311,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="36" t="s">
         <v>188</v>
       </c>
@@ -24317,7 +24334,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="38" t="s">
         <v>254</v>
       </c>
@@ -24340,7 +24357,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="34" t="s">
         <v>157</v>
       </c>
@@ -24363,7 +24380,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="34" t="s">
         <v>157</v>
       </c>
@@ -24386,7 +24403,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="34" t="s">
         <v>157</v>
       </c>
@@ -24409,7 +24426,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="34" t="s">
         <v>157</v>
       </c>
@@ -24432,7 +24449,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="36" t="s">
         <v>188</v>
       </c>
@@ -24455,7 +24472,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="36" t="s">
         <v>188</v>
       </c>
@@ -24478,7 +24495,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="38" t="s">
         <v>254</v>
       </c>
@@ -24501,7 +24518,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="36" t="s">
         <v>188</v>
       </c>
@@ -24524,7 +24541,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="36" t="s">
         <v>188</v>
       </c>
@@ -24547,7 +24564,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="36" t="s">
         <v>188</v>
       </c>
@@ -24570,7 +24587,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="36" t="s">
         <v>188</v>
       </c>
@@ -24593,7 +24610,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="36" t="s">
         <v>188</v>
       </c>
@@ -24616,7 +24633,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="36" t="s">
         <v>188</v>
       </c>
@@ -24639,7 +24656,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="36" t="s">
         <v>188</v>
       </c>
@@ -24662,7 +24679,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="36" t="s">
         <v>188</v>
       </c>
@@ -24685,7 +24702,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="36" t="s">
         <v>188</v>
       </c>
@@ -24708,7 +24725,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="36" t="s">
         <v>188</v>
       </c>
@@ -24731,7 +24748,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="36" t="s">
         <v>188</v>
       </c>
@@ -24754,7 +24771,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="36" t="s">
         <v>188</v>
       </c>
@@ -24777,7 +24794,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="36" t="s">
         <v>188</v>
       </c>
@@ -24800,7 +24817,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="38" t="s">
         <v>254</v>
       </c>
@@ -24823,7 +24840,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="38" t="s">
         <v>254</v>
       </c>
@@ -24846,7 +24863,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="38" t="s">
         <v>254</v>
       </c>
@@ -24869,7 +24886,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="34" t="s">
         <v>157</v>
       </c>
@@ -24892,7 +24909,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="34" t="s">
         <v>157</v>
       </c>
@@ -24915,7 +24932,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="34" t="s">
         <v>157</v>
       </c>
@@ -24938,7 +24955,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="32" t="s">
         <v>101</v>
       </c>
@@ -24961,7 +24978,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="20" t="s">
         <v>32</v>
       </c>
@@ -24984,7 +25001,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="20" t="s">
         <v>32</v>
       </c>
@@ -25007,7 +25024,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="20" t="s">
         <v>32</v>
       </c>
@@ -25030,7 +25047,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="20" t="s">
         <v>32</v>
       </c>
@@ -25053,7 +25070,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="20" t="s">
         <v>32</v>
       </c>
@@ -25076,7 +25093,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="38" t="s">
         <v>254</v>
       </c>
@@ -25099,7 +25116,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="38" t="s">
         <v>254</v>
       </c>
@@ -25122,7 +25139,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="36" t="s">
         <v>188</v>
       </c>
@@ -25145,7 +25162,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="36" t="s">
         <v>188</v>
       </c>
@@ -25168,7 +25185,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="38" t="s">
         <v>254</v>
       </c>
@@ -25191,7 +25208,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="38" t="s">
         <v>254</v>
       </c>
@@ -25214,7 +25231,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="38" t="s">
         <v>254</v>
       </c>
@@ -25237,7 +25254,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="32" t="s">
         <v>101</v>
       </c>
@@ -25260,7 +25277,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="32" t="s">
         <v>101</v>
       </c>
@@ -25283,7 +25300,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="38" t="s">
         <v>254</v>
       </c>
@@ -25306,7 +25323,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="20" t="s">
         <v>32</v>
       </c>
@@ -25329,7 +25346,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="20" t="s">
         <v>32</v>
       </c>
@@ -25352,7 +25369,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="20" t="s">
         <v>32</v>
       </c>
@@ -25375,7 +25392,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="20" t="s">
         <v>32</v>
       </c>
@@ -25398,7 +25415,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="20" t="s">
         <v>32</v>
       </c>
@@ -25421,7 +25438,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="34" t="s">
         <v>157</v>
       </c>
@@ -25444,7 +25461,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="34" t="s">
         <v>157</v>
       </c>
@@ -25467,7 +25484,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="34" t="s">
         <v>157</v>
       </c>
@@ -25490,7 +25507,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="38" t="s">
         <v>254</v>
       </c>
@@ -25513,7 +25530,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="38" t="s">
         <v>254</v>
       </c>
@@ -25536,7 +25553,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="38" t="s">
         <v>254</v>
       </c>
@@ -25559,7 +25576,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="38" t="s">
         <v>254</v>
       </c>
@@ -25582,7 +25599,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="32" t="s">
         <v>101</v>
       </c>
@@ -25605,7 +25622,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="32" t="s">
         <v>101</v>
       </c>
@@ -25628,7 +25645,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="20" t="s">
         <v>32</v>
       </c>
@@ -25651,7 +25668,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="20" t="s">
         <v>32</v>
       </c>
@@ -25674,7 +25691,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="20" t="s">
         <v>32</v>
       </c>
@@ -25697,7 +25714,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="20" t="s">
         <v>32</v>
       </c>
@@ -25720,7 +25737,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="20" t="s">
         <v>32</v>
       </c>
@@ -25743,7 +25760,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="20" t="s">
         <v>32</v>
       </c>
@@ -25766,7 +25783,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="20" t="s">
         <v>32</v>
       </c>
@@ -25789,7 +25806,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="32" t="s">
         <v>101</v>
       </c>
@@ -25812,7 +25829,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="20" t="s">
         <v>32</v>
       </c>
@@ -25835,7 +25852,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="38" t="s">
         <v>254</v>
       </c>
@@ -25858,7 +25875,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="32" t="s">
         <v>101</v>
       </c>
@@ -25881,7 +25898,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="32" t="s">
         <v>101</v>
       </c>
@@ -25904,7 +25921,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="32" t="s">
         <v>101</v>
       </c>
@@ -25927,7 +25944,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="34" t="s">
         <v>157</v>
       </c>
@@ -25950,7 +25967,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="34" t="s">
         <v>157</v>
       </c>
@@ -25973,7 +25990,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="34" t="s">
         <v>157</v>
       </c>
@@ -25996,7 +26013,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="32" t="s">
         <v>101</v>
       </c>
@@ -26019,7 +26036,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="32" t="s">
         <v>101</v>
       </c>
@@ -26043,7 +26060,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G451" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A3:G451" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Daltez"/>
+        <filter val="Daltez - Bimestral"/>
+        <filter val="Pedro Dalari"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -26064,7 +26089,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="67" t="s">
         <v>742</v>
       </c>
       <c r="B1" s="52"/>
@@ -26073,7 +26098,7 @@
       <c r="E1" s="52"/>
     </row>
     <row r="2" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="61" t="s">
         <v>743</v>
       </c>
       <c r="B2" s="52"/>
@@ -27735,7 +27760,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="68" t="s">
         <v>744</v>
       </c>
       <c r="B1" s="52"/>
@@ -27745,7 +27770,7 @@
       <c r="F1" s="52"/>
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="61" t="s">
         <v>745</v>
       </c>
       <c r="B2" s="52"/>
